--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/createMember-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/createMember-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
-  <si>
-    <t>Statement: UserRepository.createMember(data) – atomically creates a User and Member record. Hashes the password with bcrypt (12 rounds). Throws ConflictError if the email is already registered. Wraps any database failure in a TransactionError.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="55">
+  <si>
+    <t>Statement: UserRepository.createMember(data) – Creates a new user and member record atomically. Returns the created MemberWithUser on success. Throws ConflictError if the email is already registered. Throws TransactionError if the database write fails.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateMemberInput { email, fullName, phone, dateOfBirth, password, membershipStart }</t>
+    <t>Input: data: CreateMemberInput</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible | No User row with data.email already exists</t>
+    <t>Database is accessible. The provided email may or may not already be registered.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;MemberWithUser&gt; | throws ConflictError / TransactionError</t>
+    <t>Output: Promise&lt;MemberWithUser&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: new User + Member rows are persisted atomically, password is stored as bcrypt hash.</t>
+    <t>On success: MemberWithUser returned with result.id: MEMBER_ID and result.user defined. On failure: ConflictError or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,19 +67,19 @@
     <t>Email uniqueness</t>
   </si>
   <si>
-    <t>Email not yet registered</t>
-  </si>
-  <si>
-    <t>Email already registered (ConflictError)</t>
-  </si>
-  <si>
-    <t>Database status</t>
-  </si>
-  <si>
-    <t>Database write succeeds</t>
-  </si>
-  <si>
-    <t>Database write fails (TransactionError)</t>
+    <t>Unique email → MemberWithUser returned</t>
+  </si>
+  <si>
+    <t>Duplicate email → ConflictError</t>
+  </si>
+  <si>
+    <t>Database write</t>
+  </si>
+  <si>
+    <t>Write succeeds → MemberWithUser returned</t>
+  </si>
+  <si>
+    <t>Write fails → TransactionError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -100,10 +100,10 @@
     <t>EC-1, EC-3</t>
   </si>
   <si>
-    <t>Valid member data, unique email</t>
-  </si>
-  <si>
-    <t>Returns MemberWithUser</t>
+    <t>data: CREATE_MEMBER_INPUT, email unique, DB succeeds</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: MEMBER_ID, result.user defined</t>
   </si>
   <si>
     <t>Passed</t>
@@ -112,19 +112,19 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Valid member data, email already registered</t>
-  </si>
-  <si>
-    <t>Throws ConflictError</t>
+    <t>data: CREATE_MEMBER_INPUT, email already registered</t>
+  </si>
+  <si>
+    <t>throws ConflictError</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Valid member data, database connection fails</t>
-  </si>
-  <si>
-    <t>Throws TransactionError</t>
+    <t>data: CREATE_MEMBER_INPUT, DB throws Error("DB connection failed")</t>
+  </si>
+  <si>
+    <t>throws TransactionError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -133,51 +133,15 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Password storage</t>
-  </si>
-  <si>
-    <t>Input password plaintext vs Hashed output</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Hashing</t>
-  </si>
-  <si>
-    <t>Password="SecureP@ss1"</t>
-  </si>
-  <si>
-    <t>Stored hash exists</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>Valid member data, email not registered</t>
-  </si>
-  <si>
-    <t>Email already in use</t>
-  </si>
-  <si>
-    <t>DB write throws Error</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>Check stored password hashing</t>
-  </si>
-  <si>
-    <t>Password is bcrypt hashed</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -208,7 +172,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-01</t>
+    <t>REPO-01</t>
   </si>
   <si>
     <t>n/a</t>
@@ -774,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -802,7 +766,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -905,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -924,17 +888,6 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -943,7 +896,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -958,7 +911,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -968,23 +921,6 @@
       </c>
       <c r="E1" s="4" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +931,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1011,10 +947,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1031,13 +967,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
@@ -1057,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>32</v>
@@ -1077,32 +1013,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1131,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1148,45 +1064,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1195,19 +1111,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
